--- a/public/exports-from-60-with-coowners/68534917.xlsx
+++ b/public/exports-from-60-with-coowners/68534917.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016078</t>
+          <t xml:space="preserve">200016088</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">

--- a/public/exports-from-60-with-coowners/68534917.xlsx
+++ b/public/exports-from-60-with-coowners/68534917.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016088</t>
+          <t xml:space="preserve">200016078</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">

--- a/public/exports-from-60-with-coowners/68534917.xlsx
+++ b/public/exports-from-60-with-coowners/68534917.xlsx
@@ -1016,40 +1016,40 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 3</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203386</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J14">
-        <v>1115</v>
+        <v>1586</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047379</t>
+          <t xml:space="preserve">200055903</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grontmij A/S</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-29</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1091,40 +1091,40 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Tingsryds Alle 1B</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2203980</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J15">
-        <v>1586</v>
+        <v>1771</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055903</t>
+          <t xml:space="preserve">311156883</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 1B</t>
+          <t xml:space="preserve">Mosevej 13A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203980</t>
+          <t xml:space="preserve">2204990</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,31 +1185,31 @@
         </is>
       </c>
       <c r="J16">
-        <v>1771</v>
+        <v>250</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156883</t>
+          <t xml:space="preserve">311211526</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-03</t>
+          <t xml:space="preserve">2026-11-10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 13A</t>
+          <t xml:space="preserve">Mosevej 13B</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1256,15 +1256,15 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211526</t>
+          <t xml:space="preserve">311211741</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-10</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 13B</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,20 +1326,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204990</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J18">
-        <v>280</v>
+        <v>355</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211741</t>
+          <t xml:space="preserve">311214136</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1391,30 +1391,30 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Bistrupvang 36</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2188168</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J19">
-        <v>355</v>
+        <v>792</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214136</t>
+          <t xml:space="preserve">311217330</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 36</t>
+          <t xml:space="preserve">Karlstrupvej 54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188168</t>
+          <t xml:space="preserve">2195619</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="J20">
-        <v>792</v>
+        <v>241</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217330</t>
+          <t xml:space="preserve">311217350</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlstrupvej 54</t>
+          <t xml:space="preserve">Karlstrupvej 56</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J21">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlstrupvej 56</t>
+          <t xml:space="preserve">Poppelhegnet 32A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2195619</t>
+          <t xml:space="preserve">2203865</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217350</t>
+          <t xml:space="preserve">311217456</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelhegnet 32A</t>
+          <t xml:space="preserve">Poppelhegnet 32B</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J23">
-        <v>250</v>
+        <v>501</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,30 +1766,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelhegnet 32B</t>
+          <t xml:space="preserve">Sognevejen 7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">2690</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203865</t>
+          <t xml:space="preserve">2195673</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>501</v>
+        <v>195</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217456</t>
+          <t xml:space="preserve">311217386</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevejen 7</t>
+          <t xml:space="preserve">Solrød Center 85</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2690</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2195673</t>
+          <t xml:space="preserve">2203431</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="J25">
-        <v>195</v>
+        <v>2288</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217386</t>
+          <t xml:space="preserve">311217395</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 85</t>
+          <t xml:space="preserve">Tingsryds Alle 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203431</t>
+          <t xml:space="preserve">2203441</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="J26">
-        <v>2288</v>
+        <v>839</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217395</t>
+          <t xml:space="preserve">311217448</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 3</t>
+          <t xml:space="preserve">Tjørnholmvej 14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203441</t>
+          <t xml:space="preserve">2204105</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="J27">
-        <v>839</v>
+        <v>232</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217448</t>
+          <t xml:space="preserve">311217441</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 14</t>
+          <t xml:space="preserve">Bistrupvang 35</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204105</t>
+          <t xml:space="preserve">2188167</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,11 +2085,11 @@
         </is>
       </c>
       <c r="J28">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217441</t>
+          <t xml:space="preserve">311217631</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvang 35</t>
+          <t xml:space="preserve">Solrød Center 1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188167</t>
+          <t xml:space="preserve">2203336</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,11 +2160,11 @@
         </is>
       </c>
       <c r="J29">
-        <v>383</v>
+        <v>3581</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217631</t>
+          <t xml:space="preserve">311217669</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 1</t>
+          <t xml:space="preserve">Trylleskov Allé 3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203336</t>
+          <t xml:space="preserve">100036252</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>3581</v>
+        <v>1252</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217669</t>
+          <t xml:space="preserve">311217682</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trylleskov Allé 3</t>
+          <t xml:space="preserve">Lindevej 15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036252</t>
+          <t xml:space="preserve">2187966</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>1252</v>
+        <v>260</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217682</t>
+          <t xml:space="preserve">311217802</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2381,11 +2381,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J32">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,30 +2441,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 15</t>
+          <t xml:space="preserve">Tjørnholmvej 12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187966</t>
+          <t xml:space="preserve">2204117</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>220</v>
+        <v>875</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217802</t>
+          <t xml:space="preserve">311217827</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 12</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204117</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,11 +2535,11 @@
         </is>
       </c>
       <c r="J34">
-        <v>875</v>
+        <v>1690</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217827</t>
+          <t xml:space="preserve">311224721</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2606,15 +2606,15 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J35">
-        <v>1690</v>
+        <v>295</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224721</t>
+          <t xml:space="preserve">311224732</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2681,15 +2681,15 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J36">
-        <v>295</v>
+        <v>1384</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224732</t>
+          <t xml:space="preserve">311224734</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2756,15 +2756,15 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J37">
-        <v>1384</v>
+        <v>975</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224734</t>
+          <t xml:space="preserve">311224736</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2831,15 +2831,15 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J38">
-        <v>975</v>
+        <v>1102</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224736</t>
+          <t xml:space="preserve">311224724</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J39">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224724</t>
+          <t xml:space="preserve">311224727</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2981,15 +2981,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J40">
-        <v>1102</v>
+        <v>772</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224727</t>
+          <t xml:space="preserve">311224729</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Christians Torv 124</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">2190312</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>772</v>
+        <v>11134</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224729</t>
+          <t xml:space="preserve">311231085</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christians Torv 124</t>
+          <t xml:space="preserve">Den Lille Gade 20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,20 +3126,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190312</t>
+          <t xml:space="preserve">8942093</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J42">
-        <v>11134</v>
+        <v>718</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231085</t>
+          <t xml:space="preserve">311238100</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3206,15 +3206,15 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J43">
-        <v>718</v>
+        <v>214</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238100</t>
+          <t xml:space="preserve">311238097</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3266,30 +3266,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den Lille Gade 20</t>
+          <t xml:space="preserve">Skolevej 51</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942093</t>
+          <t xml:space="preserve">8941987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J44">
-        <v>214</v>
+        <v>308</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238097</t>
+          <t xml:space="preserve">311238368</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 51</t>
+          <t xml:space="preserve">Skolevej 53</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3356,15 +3356,15 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
-        <v>308</v>
+        <v>775</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238368</t>
+          <t xml:space="preserve">311238367</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 53</t>
+          <t xml:space="preserve">Tingsryds Alle 27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941987</t>
+          <t xml:space="preserve">8942071</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>775</v>
+        <v>11333</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238367</t>
+          <t xml:space="preserve">311238369</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingsryds Alle 27</t>
+          <t xml:space="preserve">Engmosevej 14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,15 +3506,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J47">
-        <v>11333</v>
+        <v>1724</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238369</t>
+          <t xml:space="preserve">311238574</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engmosevej 14</t>
+          <t xml:space="preserve">Lindevej 10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942071</t>
+          <t xml:space="preserve">2187862</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>1724</v>
+        <v>240</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238574</t>
+          <t xml:space="preserve">311238596</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 10</t>
+          <t xml:space="preserve">Parkvej 11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187862</t>
+          <t xml:space="preserve">2189961</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>240</v>
+        <v>719</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238596</t>
+          <t xml:space="preserve">311238422</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 11</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189961</t>
+          <t xml:space="preserve">2190233</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>719</v>
+        <v>609</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238422</t>
+          <t xml:space="preserve">311238569</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190233</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J51">
-        <v>609</v>
+        <v>1637</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238569</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J52">
-        <v>2266</v>
+        <v>2297</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3941,30 +3941,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 62</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941976</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J53">
-        <v>1889</v>
+        <v>2065</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238551</t>
+          <t xml:space="preserve">311238556</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4031,15 +4031,15 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J54">
-        <v>1637</v>
+        <v>2177</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238554</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Åsvej 14B</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942017</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>2297</v>
+        <v>2149</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238600</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,20 +4176,20 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>2065</v>
+        <v>1902</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238556</t>
+          <t xml:space="preserve">311238732</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Højagervænget 21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>2177</v>
+        <v>2493</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238554</t>
+          <t xml:space="preserve">311238734</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åsvej 14B</t>
+          <t xml:space="preserve">Højagervænget 25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,20 +4326,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942017</t>
+          <t xml:space="preserve">8942087</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J58">
-        <v>2149</v>
+        <v>137</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238600</t>
+          <t xml:space="preserve">311238742</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-04</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Langager 8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">2202814</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>1902</v>
+        <v>381</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238732</t>
+          <t xml:space="preserve">311238728</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 21</t>
+          <t xml:space="preserve">Niels Juels Alle 2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">2189963</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>2493</v>
+        <v>350</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238734</t>
+          <t xml:space="preserve">311238698</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højagervænget 25</t>
+          <t xml:space="preserve">Solrød Center 4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,20 +4551,20 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942087</t>
+          <t xml:space="preserve">267144, 267145</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>137</v>
+        <v>4890</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238742</t>
+          <t xml:space="preserve">311238723</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langager 8</t>
+          <t xml:space="preserve">Vestre Grænsevej 34</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202814</t>
+          <t xml:space="preserve">100003759</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238728</t>
+          <t xml:space="preserve">311238740</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Juels Alle 2</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189963</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>350</v>
+        <v>1789</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238698</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solrød Center 4</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">267144, 267145</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>4890</v>
+        <v>1339</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238723</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Grænsevej 34</t>
+          <t xml:space="preserve">Tjørnholmvej 10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003759</t>
+          <t xml:space="preserve">2204674</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
-        <v>431</v>
+        <v>1448</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238740</t>
+          <t xml:space="preserve">311298684</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-04</t>
+          <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Havdrup Allé 6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">7717401</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="J66">
-        <v>1789</v>
+        <v>1372</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311453702</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2030-08-11</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Vestre Odinsvej 17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,30 +5001,30 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">2203235</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>1339</v>
+        <v>339</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311519279</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2031-05-10</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,40 +5066,40 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnholmvej 10</t>
+          <t xml:space="preserve">Skolevej 70</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204674</t>
+          <t xml:space="preserve">8455708</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>1448</v>
+        <v>140</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298684</t>
+          <t xml:space="preserve">311525100</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-20</t>
+          <t xml:space="preserve">2031-06-03</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havdrup Allé 6</t>
+          <t xml:space="preserve">Salbjergvej 26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7717401</t>
+          <t xml:space="preserve">2188346</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="J69">
-        <v>1372</v>
+        <v>168</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311453702</t>
+          <t xml:space="preserve">311549329</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-11</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,40 +5216,40 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Odinsvej 17</t>
+          <t xml:space="preserve">Salbjergvej 26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203235</t>
+          <t xml:space="preserve">2188346</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311519279</t>
+          <t xml:space="preserve">311549361</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-10</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,40 +5291,40 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 70</t>
+          <t xml:space="preserve">Østre Strandvej 26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8455708</t>
+          <t xml:space="preserve">2206014</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J71">
-        <v>140</v>
+        <v>291</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525100</t>
+          <t xml:space="preserve">311668910</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+          <t xml:space="preserve">ISOLINK ApS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-03</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,40 +5366,40 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salbjergvej 26</t>
+          <t xml:space="preserve">Egeparken 33A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4622</t>
+          <t xml:space="preserve">2680</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188346</t>
+          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>168</v>
+        <v>3906</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549329</t>
+          <t xml:space="preserve">311903759</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salbjergvej 26</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,30 +5451,30 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188346</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>328</v>
+        <v>2266</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549361</t>
+          <t xml:space="preserve">311929920</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,40 +5516,40 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Strandvej 26</t>
+          <t xml:space="preserve">Skolevej 62</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2680</t>
+          <t xml:space="preserve">4622</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2206014</t>
+          <t xml:space="preserve">8941976</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
-        <v>291</v>
+        <v>1889</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668910</t>
+          <t xml:space="preserve">311929920</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISOLINK ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeparken 33A</t>
+          <t xml:space="preserve">Solrød Center 3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,30 +5601,30 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">259943, 259944, 259945, 259946, 259947, 259949, 259956, 259982, 259950, 259951, 259952, 259953, 259954, 259955, 259957, 259958, 259960, 259961, 259962, 259963, 259964, 259965, 259966, 259967, 259968, 259969, 259971, 259972, 259973, 259974, 259975, 259976, 259977, 259978, 259979, 259980, 259989, 259990, 259991, 259993, 259994, 259995</t>
+          <t xml:space="preserve">2203386</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>3906</v>
+        <v>1115</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903759</t>
+          <t xml:space="preserve">311929914</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
